--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487807_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487807_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.8016</v>
+        <v>5.9371</v>
       </c>
       <c r="E2" t="n">
-        <v>4.8947</v>
+        <v>5.4119</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9069</v>
+        <v>0.5252</v>
       </c>
       <c r="G2" t="n">
         <v>2.8343</v>
@@ -610,13 +610,13 @@
         <v>2.0812</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.1084</v>
+        <v>-0.9729</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.5658</v>
+        <v>-1.0486</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4574</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V2" t="n">
         <v>4.0757</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.5337</v>
+        <v>4.8109</v>
       </c>
       <c r="E3" t="n">
-        <v>4.8</v>
+        <v>4.9304</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2663</v>
+        <v>-0.1195</v>
       </c>
       <c r="G3" t="n">
         <v>3.1158</v>
@@ -688,13 +688,13 @@
         <v>0.6244</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0202</v>
+        <v>0.2571</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1272</v>
+        <v>0.2577</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1474</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="V3" t="n">
         <v>0.8137</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.3001</v>
+        <v>3.0938</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2103</v>
+        <v>0.7398</v>
       </c>
       <c r="F4" t="n">
-        <v>2.0898</v>
+        <v>2.354</v>
       </c>
       <c r="G4" t="n">
         <v>0.4825</v>
@@ -766,13 +766,13 @@
         <v>0.8325</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1377</v>
+        <v>-0.344</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6458</v>
+        <v>0.1753</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.7835</v>
+        <v>-0.5193</v>
       </c>
       <c r="V4" t="n">
         <v>2.1228</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.5302</v>
+        <v>3.0218</v>
       </c>
       <c r="E5" t="n">
-        <v>3.0102</v>
+        <v>3.355</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.48</v>
+        <v>-0.3332</v>
       </c>
       <c r="G5" t="n">
         <v>1.8087</v>
@@ -844,13 +844,13 @@
         <v>1.0406</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7999000000000001</v>
+        <v>-0.3083</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6524</v>
+        <v>-0.3076</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1474</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="V5" t="n">
         <v>1.5213</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.1541</v>
+        <v>2.7757</v>
       </c>
       <c r="E6" t="n">
-        <v>4.4465</v>
+        <v>4.8332</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.2925</v>
+        <v>-2.0576</v>
       </c>
       <c r="G6" t="n">
         <v>2.9185</v>
@@ -922,13 +922,13 @@
         <v>1.8731</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.937</v>
+        <v>-1.3154</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8482</v>
+        <v>-0.4615</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.0888</v>
+        <v>-0.8539</v>
       </c>
       <c r="V6" t="n">
         <v>-0.7005</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4877</v>
+        <v>0.6345</v>
       </c>
       <c r="E7" t="n">
         <v>2.1781</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.6903</v>
+        <v>-1.5435</v>
       </c>
       <c r="G7" t="n">
         <v>2.3246</v>
@@ -1000,13 +1000,13 @@
         <v>0.2081</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8774999999999999</v>
+        <v>-0.7307</v>
       </c>
       <c r="T7" t="n">
         <v>-0.261</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6165</v>
+        <v>-0.4697</v>
       </c>
       <c r="V7" t="n">
         <v>-1.1675</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.7554</v>
+        <v>-1.5639</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7085</v>
+        <v>-0.4289</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.0469</v>
+        <v>-1.135</v>
       </c>
       <c r="G10" t="n">
         <v>1.9547</v>
@@ -1234,13 +1234,13 @@
         <v>1.6649</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.5527</v>
+        <v>-1.3612</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.0439</v>
+        <v>-0.7643</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5088</v>
+        <v>-0.5969</v>
       </c>
       <c r="V10" t="n">
         <v>-0.7005</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.3567</v>
+        <v>-2.2915</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.5592</v>
+        <v>-1.494</v>
       </c>
       <c r="F11" t="n">
         <v>-0.7975</v>
@@ -1312,10 +1312,10 @@
         <v>0.2081</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1305</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1305</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.8933</v>
+        <v>-2.754</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.899</v>
+        <v>-0.5542</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.9943</v>
+        <v>-2.1998</v>
       </c>
       <c r="G12" t="n">
         <v>-0.4622</v>
@@ -1390,13 +1390,13 @@
         <v>1.8731</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8357</v>
+        <v>-0.6964</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0439</v>
+        <v>-0.6991000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2082</v>
+        <v>0.0027</v>
       </c>
       <c r="V12" t="n">
         <v>-0.3467</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.4042</v>
+        <v>-4.2881</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.945</v>
+        <v>-2.5646</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.4592</v>
+        <v>-1.7235</v>
       </c>
       <c r="G13" t="n">
         <v>-4.0619</v>
@@ -1468,13 +1468,13 @@
         <v>2.0812</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2662</v>
+        <v>-1.15</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0066</v>
+        <v>-0.6262</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2596</v>
+        <v>-0.5238</v>
       </c>
       <c r="V13" t="n">
         <v>-0.1168</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.196799999999998</v>
+        <v>8.175300000000002</v>
       </c>
       <c r="E14" t="n">
-        <v>14.2571</v>
+        <v>15.2357</v>
       </c>
       <c r="F14" t="n">
-        <v>-7.060300000000001</v>
+        <v>-7.0604</v>
       </c>
       <c r="G14" t="n">
         <v>8.326800000000002</v>
@@ -1546,13 +1546,13 @@
         <v>12.4872</v>
       </c>
       <c r="S14" t="n">
-        <v>-7.796199999999999</v>
+        <v>-6.817399999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-4.9097</v>
+        <v>-3.9309</v>
       </c>
       <c r="U14" t="n">
-        <v>-2.8864</v>
+        <v>-2.8863</v>
       </c>
       <c r="V14" t="n">
         <v>5.6253</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.92</v>
+        <v>5.2914</v>
       </c>
       <c r="E15" t="n">
-        <v>3.9643</v>
+        <v>4.0714</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9557</v>
+        <v>1.22</v>
       </c>
       <c r="G15" t="n">
         <v>4.1685</v>
@@ -1624,13 +1624,13 @@
         <v>1.6649</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3438</v>
+        <v>0.7151999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3295</v>
+        <v>-0.2224</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6733</v>
+        <v>0.9376</v>
       </c>
       <c r="V15" t="n">
         <v>1.8645</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.9818</v>
+        <v>2.5913</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6686</v>
+        <v>0.4543</v>
       </c>
       <c r="F16" t="n">
-        <v>2.3131</v>
+        <v>2.137</v>
       </c>
       <c r="G16" t="n">
         <v>0.0506</v>
@@ -1702,13 +1702,13 @@
         <v>1.6649</v>
       </c>
       <c r="S16" t="n">
-        <v>1.588</v>
+        <v>1.1975</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5806</v>
+        <v>0.3663</v>
       </c>
       <c r="U16" t="n">
-        <v>1.0074</v>
+        <v>0.8312</v>
       </c>
       <c r="V16" t="n">
         <v>0.9268999999999999</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. PA MOR</t>
+          <t>C. JACOBS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.881</v>
+        <v>1.2489</v>
       </c>
       <c r="E17" t="n">
-        <v>3.3505</v>
+        <v>0.4914</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.4695</v>
+        <v>0.7575</v>
       </c>
       <c r="G17" t="n">
-        <v>1.916</v>
+        <v>-0.4621</v>
       </c>
       <c r="H17" t="n">
-        <v>2.5756</v>
+        <v>-0.5821</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.6597</v>
+        <v>0.12</v>
       </c>
       <c r="J17" t="n">
-        <v>3.0837</v>
+        <v>0.5628</v>
       </c>
       <c r="K17" t="n">
-        <v>2.927</v>
+        <v>-0.5165</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1568</v>
+        <v>1.0793</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.1678</v>
+        <v>-1.0249</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3513</v>
+        <v>-0.06560000000000001</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.8164</v>
+        <v>-0.9593</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.4568</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.0406</v>
+        <v>1.4568</v>
       </c>
       <c r="S17" t="n">
-        <v>2.6468</v>
+        <v>0.608</v>
       </c>
       <c r="T17" t="n">
-        <v>1.3073</v>
+        <v>0.2824</v>
       </c>
       <c r="U17" t="n">
-        <v>1.3395</v>
+        <v>0.3256</v>
       </c>
       <c r="V17" t="n">
-        <v>-2.6818</v>
+        <v>-0.3538</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>-0.3538</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.6818</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C. JACOBS</t>
+          <t>D. PA MOR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1275</v>
+        <v>0.7492</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.3658</v>
+        <v>2.6004</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4933</v>
+        <v>-1.8511</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.4621</v>
+        <v>1.916</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5821</v>
+        <v>2.5756</v>
       </c>
       <c r="I18" t="n">
-        <v>0.12</v>
+        <v>-0.6597</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5628</v>
+        <v>3.0837</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.5165</v>
+        <v>2.927</v>
       </c>
       <c r="L18" t="n">
-        <v>1.0793</v>
+        <v>0.1568</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.0249</v>
+        <v>-1.1678</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.06560000000000001</v>
+        <v>-0.3513</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.9593</v>
+        <v>-0.8164</v>
       </c>
       <c r="P18" t="n">
-        <v>1.4568</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R18" t="n">
-        <v>1.4568</v>
+        <v>1.0406</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5134</v>
+        <v>1.515</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5748</v>
+        <v>0.5573</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0614</v>
+        <v>0.9578</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.3538</v>
+        <v>-2.6818</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.3538</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-2.6818</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3886</v>
+        <v>-0.0172</v>
       </c>
       <c r="E19" t="n">
-        <v>2.398</v>
+        <v>2.5051</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.7865</v>
+        <v>-2.5223</v>
       </c>
       <c r="G19" t="n">
         <v>-3.1307</v>
@@ -1936,13 +1936,13 @@
         <v>0.8325</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1005</v>
+        <v>0.2709</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2643</v>
+        <v>-0.1571</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1638</v>
+        <v>0.428</v>
       </c>
       <c r="V19" t="n">
         <v>2.2183</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.6329</v>
+        <v>-0.5845</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2219</v>
+        <v>0.329</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.8548</v>
+        <v>-0.9135</v>
       </c>
       <c r="G20" t="n">
         <v>-2.2711</v>
@@ -2014,13 +2014,13 @@
         <v>1.6649</v>
       </c>
       <c r="S20" t="n">
-        <v>1.222</v>
+        <v>1.2704</v>
       </c>
       <c r="T20" t="n">
-        <v>0.7887</v>
+        <v>0.8959</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4332</v>
+        <v>0.3745</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.19</v>
+        <v>-1.3621</v>
       </c>
       <c r="E21" t="n">
-        <v>1.6322</v>
+        <v>2.4894</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.8222</v>
+        <v>-3.8516</v>
       </c>
       <c r="G21" t="n">
         <v>-0.773</v>
@@ -2092,13 +2092,13 @@
         <v>0.6244</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4358</v>
+        <v>0.3921</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3791</v>
+        <v>0.4782</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0567</v>
+        <v>-0.0861</v>
       </c>
       <c r="V21" t="n">
         <v>-1.3975</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.963</v>
+        <v>-3.8749</v>
       </c>
       <c r="E22" t="n">
         <v>-1.3965</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.5665</v>
+        <v>-2.4785</v>
       </c>
       <c r="G22" t="n">
         <v>-1.7855</v>
@@ -2170,13 +2170,13 @@
         <v>0.6244</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4469</v>
+        <v>0.535</v>
       </c>
       <c r="T22" t="n">
         <v>0.3229</v>
       </c>
       <c r="U22" t="n">
-        <v>0.124</v>
+        <v>0.212</v>
       </c>
       <c r="V22" t="n">
         <v>-1.1675</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.1921</v>
+        <v>-5.0509</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.2972</v>
+        <v>-0.8329</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.895</v>
+        <v>-4.2179</v>
       </c>
       <c r="G23" t="n">
         <v>-2.373</v>
@@ -2248,13 +2248,13 @@
         <v>0.6244</v>
       </c>
       <c r="S23" t="n">
-        <v>1.5149</v>
+        <v>0.6562</v>
       </c>
       <c r="T23" t="n">
-        <v>0.9068000000000001</v>
+        <v>0.371</v>
       </c>
       <c r="U23" t="n">
-        <v>0.6081</v>
+        <v>0.2851</v>
       </c>
       <c r="V23" t="n">
         <v>-3.7503</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.7402</v>
+        <v>-6.1879</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.1157</v>
+        <v>-3.6515</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.6246</v>
+        <v>-2.5365</v>
       </c>
       <c r="G24" t="n">
         <v>-3.6665</v>
@@ -2326,13 +2326,13 @@
         <v>1.2487</v>
       </c>
       <c r="S24" t="n">
-        <v>1.0836</v>
+        <v>0.6359</v>
       </c>
       <c r="T24" t="n">
-        <v>0.5276999999999999</v>
+        <v>-0.008</v>
       </c>
       <c r="U24" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.644</v>
       </c>
       <c r="V24" t="n">
         <v>-1.2843</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.1965</v>
+        <v>-7.1967</v>
       </c>
       <c r="E25" t="n">
-        <v>7.0603</v>
+        <v>7.060099999999998</v>
       </c>
       <c r="F25" t="n">
-        <v>-14.257</v>
+        <v>-14.2569</v>
       </c>
       <c r="G25" t="n">
         <v>-8.3268</v>
@@ -2404,13 +2404,13 @@
         <v>11.4465</v>
       </c>
       <c r="S25" t="n">
-        <v>7.7963</v>
+        <v>7.796200000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>2.8863</v>
+        <v>2.8865</v>
       </c>
       <c r="U25" t="n">
-        <v>4.9099</v>
+        <v>4.9097</v>
       </c>
       <c r="V25" t="n">
         <v>-5.625500000000001</v>
